--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:44</t>
+    <t xml:space="preserve">2026-09-09 23:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:44</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1120,8 +1120,12 @@
       <c r="C34" s="2" t="n">
         <v>6204</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="D34" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>64125.91</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:32</t>
+    <t xml:space="preserve">2026-09-23 13:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:04</t>
+    <t xml:space="preserve">2026-10-02 14:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:52</t>
+    <t xml:space="preserve">2026-10-04 09:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:50</t>
+    <t xml:space="preserve">2026-10-05 13:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -767,7 +767,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>72619.62</v>
+        <v>72619.63</v>
       </c>
     </row>
     <row r="14">
@@ -835,7 +835,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>71339.62</v>
+        <v>71339.63</v>
       </c>
     </row>
     <row r="18">
